--- a/source_file/table_for_github.xlsx
+++ b/source_file/table_for_github.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahramhan/Dropbox/CVD VE review/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/code/ecgfm/my_repo/ECGPPG_FM_dataset/source_file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55311777-E179-F64E-8FE0-91AE30E4365B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA719599-0AFF-AE4B-9EA2-57535E93CC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{B2F66E05-8131-1E48-866D-739C3566B599}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{B2F66E05-8131-1E48-866D-739C3566B599}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1222,7 +1222,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1312,13 +1312,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1808,7 +1805,7 @@
       <c r="P2" s="27">
         <v>8</v>
       </c>
-      <c r="Q2" s="34">
+      <c r="Q2" s="33">
         <v>250</v>
       </c>
       <c r="R2" s="20">
@@ -1891,7 +1888,7 @@
       <c r="P3" s="12">
         <v>12</v>
       </c>
-      <c r="Q3" s="34">
+      <c r="Q3" s="33">
         <v>100</v>
       </c>
       <c r="R3" s="20">
@@ -1974,7 +1971,7 @@
       <c r="P4" s="12">
         <v>12</v>
       </c>
-      <c r="Q4" s="34" t="s">
+      <c r="Q4" s="33" t="s">
         <v>187</v>
       </c>
       <c r="R4" s="20">
@@ -2057,7 +2054,7 @@
       <c r="P5" s="12">
         <v>12</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="33">
         <v>500</v>
       </c>
       <c r="R5" s="20">
@@ -2140,7 +2137,7 @@
       <c r="P6" s="12">
         <v>12</v>
       </c>
-      <c r="Q6" s="34">
+      <c r="Q6" s="33">
         <v>100</v>
       </c>
       <c r="R6" s="20">
@@ -2223,7 +2220,7 @@
       <c r="P7" s="12">
         <v>12</v>
       </c>
-      <c r="Q7" s="34">
+      <c r="Q7" s="33">
         <v>240</v>
       </c>
       <c r="R7" s="20">
@@ -2283,7 +2280,7 @@
         <v>119</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J8" s="25" t="s">
         <v>106</v>
@@ -2306,7 +2303,7 @@
       <c r="P8" s="12">
         <v>12</v>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="33">
         <v>500</v>
       </c>
       <c r="R8" s="20">
@@ -2366,7 +2363,7 @@
         <v>119</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J9" s="25" t="s">
         <v>123</v>
@@ -2718,7 +2715,7 @@
       <c r="O13" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="P13" s="31">
+      <c r="P13" s="29">
         <v>1</v>
       </c>
       <c r="Q13" s="18">
@@ -2801,7 +2798,7 @@
       <c r="O14" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="P14" s="32" t="s">
+      <c r="P14" s="31" t="s">
         <v>190</v>
       </c>
       <c r="Q14" s="18">
@@ -2881,10 +2878,10 @@
       <c r="N15" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="O15" s="33" t="s">
+      <c r="O15" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="29">
         <v>1</v>
       </c>
       <c r="Q15" s="18">
@@ -2967,7 +2964,7 @@
       <c r="O16" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="P16" s="32" t="s">
+      <c r="P16" s="31" t="s">
         <v>190</v>
       </c>
       <c r="Q16" s="18">
@@ -3047,10 +3044,10 @@
       <c r="N17" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="O17" s="33" t="s">
+      <c r="O17" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="P17" s="32" t="s">
+      <c r="P17" s="31" t="s">
         <v>190</v>
       </c>
       <c r="Q17" s="18">
